--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/loytel.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/loytel.xlsx
@@ -4964,7 +4964,7 @@
   </si>
   <si>
     <t xml:space="preserve">我也不信。虽然凯特尔身上确实是有许多谜团，听了你的话后，我也会有些怀疑他是不是真的「人类」。
-不过我都实际见过了龙之子、魔女之子，还和一块飘在半空的破布似的幽灵聊过天，也算是什么事都见怪不怪了…诶呀，用破布来称呼你实在有点失礼了。</t>
+不过我都实际见过了龙之子、魔女之子，还和一块飘在半空的破布似的幽灵聊过天，也算是什么事都见怪不怪了…哎呀，用破布来称呼你实在有点失礼了。</t>
   </si>
   <si>
     <t xml:space="preserve">…想怎么称呼都随你。</t>
